--- a/simulation/biogas/biogas_economics.xlsx
+++ b/simulation/biogas/biogas_economics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Propanol production\simulation\biogas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06D57AC-B11C-4106-96CB-95E471267628}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68DCAE4-9D45-4628-AD46-FFE906305A07}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="21600" windowHeight="8430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="21600" windowHeight="8430" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -930,7 +930,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1109,6 +1109,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4122,7 +4123,7 @@
         <f>D5*E5</f>
         <v>1905.4350212216154</v>
       </c>
-      <c r="G5" s="36"/>
+      <c r="G5" s="70"/>
       <c r="K5" s="25">
         <v>90.02</v>
       </c>
@@ -4524,6 +4525,7 @@
       <c r="B19" s="8" t="s">
         <v>66</v>
       </c>
+      <c r="E19" s="18"/>
       <c r="H19" s="55" t="s">
         <v>131</v>
       </c>
